--- a/outputs/barcelona_samples_2019_2023_filled.xlsx
+++ b/outputs/barcelona_samples_2019_2023_filled.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ADD" sheetId="1" state="visible" r:id="rId3"/>
@@ -599,7 +599,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -610,6 +610,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF7CC"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -647,7 +653,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -665,6 +671,22 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3106,38 +3128,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
+    <row r="33" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="1" t="s">
+      <c r="B33" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="E33" s="5" t="n">
         <v>2.13808882764804</v>
       </c>
-      <c r="F33" s="1" t="n">
+      <c r="F33" s="5" t="n">
         <v>41.3854551096854</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="H33" s="3" t="str">
+      <c r="H33" s="6" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3854551096854,2.13808882764804","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I33" s="4" t="s">
+      <c r="I33" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="J33" s="4" t="s">
+      <c r="J33" s="7" t="s">
         <v>35</v>
       </c>
+      <c r="K33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
